--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$295</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9158" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,6 +991,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Observation.value.qualifier</t>
   </si>
   <si>
@@ -1204,6 +1208,12 @@
   </si>
   <si>
     <t>ParticipantRole.code</t>
+  </si>
+  <si>
+    <t>Observation.participant.participantRole.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>ParticipantRole.sdtcSpecialty</t>
   </si>
   <si>
     <t>Observation.participant.participantRole.addr</t>
@@ -2350,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK294"/>
+  <dimension ref="A1:AK295"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="76.65234375" customWidth="true" bestFit="true"/>
@@ -12191,7 +12201,7 @@
         <v>74</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>74</v>
@@ -12199,10 +12209,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12302,10 +12312,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12405,10 +12415,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12464,25 +12474,25 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -12502,10 +12512,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12561,25 +12571,25 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -12599,10 +12609,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12629,7 +12639,7 @@
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12680,7 +12690,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -12700,10 +12710,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12726,7 +12736,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12779,7 +12789,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12799,10 +12809,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12825,7 +12835,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12878,7 +12888,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12898,10 +12908,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12924,7 +12934,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12977,7 +12987,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12997,10 +13007,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13023,7 +13033,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -13076,7 +13086,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -13096,10 +13106,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13122,7 +13132,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -13175,7 +13185,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -13195,10 +13205,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13221,13 +13231,13 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13278,7 +13288,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -13298,10 +13308,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13399,10 +13409,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13500,10 +13510,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13601,10 +13611,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13702,10 +13712,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13805,10 +13815,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13908,10 +13918,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14011,10 +14021,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14114,10 +14124,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14215,10 +14225,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14255,7 +14265,7 @@
         <v>74</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>74</v>
@@ -14274,7 +14284,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>74</v>
@@ -14292,7 +14302,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
@@ -14312,10 +14322,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14349,7 +14359,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>74</v>
@@ -14371,7 +14381,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>74</v>
@@ -14389,7 +14399,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -14409,10 +14419,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14488,7 +14498,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -14508,10 +14518,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14587,7 +14597,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14607,10 +14617,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14686,7 +14696,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14706,10 +14716,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14732,7 +14742,7 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14785,7 +14795,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
@@ -14805,10 +14815,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14906,10 +14916,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15007,10 +15017,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15108,10 +15118,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15209,10 +15219,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15312,10 +15322,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15415,10 +15425,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15518,10 +15528,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15621,10 +15631,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15722,10 +15732,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15755,14 +15765,14 @@
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>74</v>
@@ -15781,7 +15791,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -15799,7 +15809,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15819,10 +15829,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15898,7 +15908,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15918,10 +15928,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15944,7 +15954,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15997,7 +16007,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -16017,10 +16027,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16076,7 +16086,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>74</v>
@@ -16094,7 +16104,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -16114,10 +16124,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16140,7 +16150,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>388</v>
+        <v>257</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -16239,7 +16249,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>311</v>
+        <v>391</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16292,7 +16302,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -16312,10 +16322,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16326,7 +16336,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>74</v>
@@ -16338,7 +16348,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>393</v>
+        <v>311</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16397,7 +16407,7 @@
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>74</v>
@@ -16422,7 +16432,7 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>75</v>
@@ -16519,11 +16529,9 @@
       <c r="D140" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E140" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>75</v>
@@ -16538,12 +16546,10 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="L140" s="2"/>
-      <c r="M140" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -16569,11 +16575,13 @@
         <v>74</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>74</v>
@@ -16591,7 +16599,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>89</v>
+        <v>400</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16611,21 +16619,23 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E141" s="2"/>
+      <c r="E141" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>74</v>
@@ -16637,11 +16647,11 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -16668,13 +16678,11 @@
         <v>74</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>74</v>
@@ -16692,13 +16700,13 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>74</v>
@@ -16712,10 +16720,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16726,7 +16734,7 @@
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>74</v>
@@ -16738,11 +16746,11 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16793,19 +16801,19 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>74</v>
@@ -16813,18 +16821,16 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E143" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>80</v>
       </c>
@@ -16841,11 +16847,11 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16872,11 +16878,13 @@
         <v>74</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y143" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z143" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>74</v>
@@ -16894,7 +16902,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16906,7 +16914,7 @@
         <v>74</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>74</v>
@@ -16914,17 +16922,17 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F144" t="s" s="2">
         <v>80</v>
@@ -16942,11 +16950,11 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16973,13 +16981,11 @@
         <v>74</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>74</v>
@@ -16997,7 +17003,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -17017,17 +17023,17 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F145" t="s" s="2">
         <v>80</v>
@@ -17045,11 +17051,11 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -17100,7 +17106,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -17120,20 +17126,20 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F146" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>75</v>
@@ -17148,11 +17154,11 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -17161,7 +17167,7 @@
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>74</v>
@@ -17203,7 +17209,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -17223,17 +17229,17 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F147" t="s" s="2">
         <v>75</v>
@@ -17251,11 +17257,11 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -17264,7 +17270,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>74</v>
@@ -17306,7 +17312,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -17326,21 +17332,23 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F148" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>74</v>
@@ -17352,11 +17360,11 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -17407,13 +17415,13 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>74</v>
@@ -17427,10 +17435,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17441,7 +17449,7 @@
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>74</v>
@@ -17453,21 +17461,23 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L149" s="2"/>
-      <c r="M149" s="2"/>
+      <c r="M149" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
-        <v>408</v>
+        <v>74</v>
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>409</v>
+        <v>74</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>74</v>
@@ -17482,11 +17492,13 @@
         <v>74</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y149" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>410</v>
+        <v>74</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>74</v>
@@ -17504,13 +17516,13 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>411</v>
+        <v>125</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>74</v>
@@ -17524,10 +17536,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17557,14 +17569,14 @@
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>74</v>
+        <v>411</v>
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
-        <v>413</v>
+        <v>74</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>74</v>
+        <v>412</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>74</v>
@@ -17583,25 +17595,25 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17621,10 +17633,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17632,7 +17644,7 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>75</v>
@@ -17647,14 +17659,10 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L151" s="2"/>
+      <c r="M151" s="2"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -17662,7 +17670,7 @@
       </c>
       <c r="Q151" s="2"/>
       <c r="R151" t="s" s="2">
-        <v>74</v>
+        <v>416</v>
       </c>
       <c r="S151" t="s" s="2">
         <v>74</v>
@@ -17680,11 +17688,11 @@
         <v>74</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>258</v>
+        <v>87</v>
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>74</v>
@@ -17702,7 +17710,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17722,20 +17730,18 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E152" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>75</v>
@@ -17750,11 +17756,13 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L152" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="M152" t="s" s="2">
-        <v>86</v>
+        <v>421</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17781,11 +17789,11 @@
         <v>74</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>88</v>
+        <v>422</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>74</v>
@@ -17803,7 +17811,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>89</v>
+        <v>423</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17823,17 +17831,17 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F153" t="s" s="2">
         <v>80</v>
@@ -17855,7 +17863,7 @@
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>195</v>
+        <v>86</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17882,13 +17890,11 @@
         <v>74</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>74</v>
@@ -17906,7 +17912,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>196</v>
+        <v>89</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17926,17 +17932,17 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>80</v>
@@ -17954,11 +17960,11 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -18009,7 +18015,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -18029,17 +18035,17 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>80</v>
@@ -18057,11 +18063,11 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -18112,7 +18118,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -18132,17 +18138,17 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F156" t="s" s="2">
         <v>80</v>
@@ -18164,7 +18170,7 @@
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -18215,7 +18221,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -18235,17 +18241,17 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F157" t="s" s="2">
         <v>80</v>
@@ -18267,7 +18273,7 @@
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -18318,7 +18324,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -18338,16 +18344,18 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E158" s="2"/>
+      <c r="E158" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="F158" t="s" s="2">
         <v>80</v>
       </c>
@@ -18364,11 +18372,11 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>214</v>
+        <v>102</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -18419,7 +18427,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -18439,10 +18447,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18465,11 +18473,11 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -18520,7 +18528,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18540,20 +18548,18 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E160" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>75</v>
@@ -18568,11 +18574,11 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18623,7 +18629,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18643,20 +18649,20 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="F161" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>75</v>
@@ -18671,11 +18677,11 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" t="s" s="2">
-        <v>86</v>
+        <v>223</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -18702,11 +18708,13 @@
         <v>74</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y161" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z161" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>74</v>
@@ -18724,7 +18732,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>89</v>
+        <v>224</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18744,17 +18752,17 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="F162" t="s" s="2">
         <v>80</v>
@@ -18776,7 +18784,7 @@
       </c>
       <c r="L162" s="2"/>
       <c r="M162" t="s" s="2">
-        <v>279</v>
+        <v>86</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18807,7 +18815,7 @@
       </c>
       <c r="Y162" s="2"/>
       <c r="Z162" t="s" s="2">
-        <v>280</v>
+        <v>88</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>74</v>
@@ -18825,7 +18833,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>281</v>
+        <v>89</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18845,17 +18853,17 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F163" t="s" s="2">
         <v>80</v>
@@ -18873,11 +18881,11 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>284</v>
+        <v>85</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18904,13 +18912,11 @@
         <v>74</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y163" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>74</v>
@@ -18928,7 +18934,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18948,17 +18954,17 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F164" t="s" s="2">
         <v>80</v>
@@ -18976,11 +18982,11 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>85</v>
+        <v>284</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -19007,11 +19013,13 @@
         <v>74</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>290</v>
+        <v>74</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>74</v>
@@ -19029,7 +19037,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -19049,17 +19057,17 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F165" t="s" s="2">
         <v>80</v>
@@ -19081,7 +19089,7 @@
       </c>
       <c r="L165" s="2"/>
       <c r="M165" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -19108,13 +19116,11 @@
         <v>74</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>74</v>
@@ -19132,7 +19138,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -19152,17 +19158,17 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>80</v>
@@ -19184,7 +19190,7 @@
       </c>
       <c r="L166" s="2"/>
       <c r="M166" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -19211,11 +19217,13 @@
         <v>74</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Y166" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z166" t="s" s="2">
-        <v>299</v>
+        <v>74</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>74</v>
@@ -19233,7 +19241,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -19253,16 +19261,18 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E167" s="2"/>
+      <c r="E167" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="F167" t="s" s="2">
         <v>80</v>
       </c>
@@ -19282,7 +19292,9 @@
         <v>85</v>
       </c>
       <c r="L167" s="2"/>
-      <c r="M167" s="2"/>
+      <c r="M167" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -19308,11 +19320,11 @@
         <v>74</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>74</v>
@@ -19330,7 +19342,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -19350,10 +19362,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19376,17 +19388,11 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L168" s="2"/>
+      <c r="M168" s="2"/>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>74</v>
@@ -19411,13 +19417,11 @@
         <v>74</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>74</v>
+        <v>302</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>74</v>
@@ -19435,7 +19439,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -19455,20 +19459,18 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E169" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>75</v>
@@ -19483,13 +19485,17 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="L169" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="M169" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N169" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>74</v>
@@ -19538,7 +19544,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -19558,20 +19564,20 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F170" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>75</v>
@@ -19586,11 +19592,11 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -19641,7 +19647,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19661,23 +19667,23 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="F171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>74</v>
@@ -19689,11 +19695,11 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" t="s" s="2">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19744,19 +19750,19 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>229</v>
+        <v>317</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>74</v>
@@ -19764,23 +19770,23 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>74</v>
@@ -19792,11 +19798,11 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19847,7 +19853,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -19867,16 +19873,18 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E173" s="2"/>
+      <c r="E173" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="F173" t="s" s="2">
         <v>80</v>
       </c>
@@ -19893,10 +19901,12 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>443</v>
+        <v>189</v>
       </c>
       <c r="L173" s="2"/>
-      <c r="M173" s="2"/>
+      <c r="M173" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -19946,7 +19956,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>444</v>
+        <v>233</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -19980,7 +19990,7 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>74</v>
@@ -19994,9 +20004,7 @@
       <c r="K174" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L174" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -20047,7 +20055,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -20067,10 +20075,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20093,12 +20101,12 @@
         <v>74</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L175" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L175" s="2"/>
-      <c r="M175" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -20148,13 +20156,13 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>74</v>
@@ -20168,10 +20176,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20194,10 +20202,12 @@
         <v>74</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>222</v>
+        <v>453</v>
       </c>
       <c r="L176" s="2"/>
-      <c r="M176" s="2"/>
+      <c r="M176" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20247,7 +20257,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -20267,10 +20277,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20293,7 +20303,7 @@
         <v>74</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>456</v>
+        <v>222</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -20380,10 +20390,10 @@
         <v>80</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>74</v>
@@ -20433,23 +20443,25 @@
         <v>74</v>
       </c>
       <c r="AB178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF178" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AC178" s="2"/>
-      <c r="AD178" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>74</v>
@@ -20466,11 +20478,9 @@
         <v>461</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>74</v>
       </c>
@@ -20482,7 +20492,7 @@
         <v>81</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>74</v>
@@ -20491,11 +20501,9 @@
         <v>74</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="L179" s="2"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -20534,19 +20542,17 @@
         <v>74</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="AC179" s="2"/>
       <c r="AD179" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -20569,20 +20575,20 @@
         <v>464</v>
       </c>
       <c r="B180" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E180" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>74</v>
@@ -20594,12 +20600,12 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L180" s="2"/>
-      <c r="M180" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -20625,11 +20631,13 @@
         <v>74</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y180" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z180" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>74</v>
@@ -20647,13 +20655,13 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>89</v>
+        <v>461</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>74</v>
@@ -20667,21 +20675,23 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E181" s="2"/>
+      <c r="E181" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>74</v>
@@ -20693,11 +20703,11 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -20724,13 +20734,11 @@
         <v>74</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>74</v>
@@ -20748,13 +20756,13 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>74</v>
@@ -20768,10 +20776,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20782,7 +20790,7 @@
         <v>80</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>74</v>
@@ -20794,11 +20802,11 @@
         <v>74</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -20849,19 +20857,19 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>74</v>
@@ -20869,18 +20877,16 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E183" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>80</v>
       </c>
@@ -20897,11 +20903,11 @@
         <v>74</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20928,11 +20934,13 @@
         <v>74</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y183" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z183" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>74</v>
@@ -20950,7 +20958,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20962,7 +20970,7 @@
         <v>74</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>74</v>
@@ -20970,17 +20978,17 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F184" t="s" s="2">
         <v>80</v>
@@ -20998,11 +21006,11 @@
         <v>74</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -21029,13 +21037,11 @@
         <v>74</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y184" s="2"/>
       <c r="Z184" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>74</v>
@@ -21053,7 +21059,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -21073,17 +21079,17 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F185" t="s" s="2">
         <v>80</v>
@@ -21101,11 +21107,11 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -21156,7 +21162,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -21176,20 +21182,20 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F186" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>75</v>
@@ -21204,11 +21210,11 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -21217,7 +21223,7 @@
       </c>
       <c r="Q186" s="2"/>
       <c r="R186" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S186" t="s" s="2">
         <v>74</v>
@@ -21259,7 +21265,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -21279,17 +21285,17 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F187" t="s" s="2">
         <v>75</v>
@@ -21307,11 +21313,11 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -21320,7 +21326,7 @@
       </c>
       <c r="Q187" s="2"/>
       <c r="R187" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S187" t="s" s="2">
         <v>74</v>
@@ -21362,7 +21368,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -21382,21 +21388,23 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E188" s="2"/>
+      <c r="E188" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F188" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>74</v>
@@ -21408,11 +21416,11 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -21463,13 +21471,13 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>74</v>
@@ -21483,10 +21491,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21494,10 +21502,10 @@
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>74</v>
@@ -21509,10 +21517,12 @@
         <v>74</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L189" s="2"/>
-      <c r="M189" s="2"/>
+      <c r="M189" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -21523,7 +21533,7 @@
         <v>74</v>
       </c>
       <c r="S189" t="s" s="2">
-        <v>484</v>
+        <v>74</v>
       </c>
       <c r="T189" t="s" s="2">
         <v>74</v>
@@ -21538,11 +21548,13 @@
         <v>74</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y189" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z189" t="s" s="2">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>74</v>
@@ -21560,13 +21572,13 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>486</v>
+        <v>125</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>74</v>
@@ -21580,10 +21592,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21591,7 +21603,7 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G190" t="s" s="2">
         <v>75</v>
@@ -21606,12 +21618,10 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L190" s="2"/>
-      <c r="M190" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="M190" s="2"/>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -21622,7 +21632,7 @@
         <v>74</v>
       </c>
       <c r="S190" t="s" s="2">
-        <v>74</v>
+        <v>487</v>
       </c>
       <c r="T190" t="s" s="2">
         <v>74</v>
@@ -21637,13 +21647,11 @@
         <v>74</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>74</v>
+        <v>488</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>74</v>
@@ -21661,10 +21669,10 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>75</v>
@@ -21681,10 +21689,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21711,12 +21719,12 @@
       </c>
       <c r="L191" s="2"/>
       <c r="M191" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
-        <v>494</v>
+        <v>74</v>
       </c>
       <c r="Q191" s="2"/>
       <c r="R191" t="s" s="2">
@@ -21762,7 +21770,7 @@
         <v>74</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -21782,10 +21790,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21811,11 +21819,13 @@
         <v>107</v>
       </c>
       <c r="L192" s="2"/>
-      <c r="M192" s="2"/>
+      <c r="M192" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
@@ -21907,7 +21917,7 @@
         <v>74</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>501</v>
+        <v>107</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21960,7 +21970,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -21980,10 +21990,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22006,7 +22016,7 @@
         <v>74</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -22059,7 +22069,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -22079,10 +22089,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22105,7 +22115,7 @@
         <v>74</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -22158,7 +22168,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -22178,10 +22188,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B196" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22204,7 +22214,7 @@
         <v>74</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -22257,7 +22267,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -22277,10 +22287,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22303,7 +22313,7 @@
         <v>74</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -22356,7 +22366,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -22376,10 +22386,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B198" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22402,7 +22412,7 @@
         <v>74</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22455,7 +22465,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -22475,10 +22485,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22501,7 +22511,7 @@
         <v>74</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22554,7 +22564,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22574,10 +22584,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22600,7 +22610,7 @@
         <v>74</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22653,7 +22663,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22673,10 +22683,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B201" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22699,7 +22709,7 @@
         <v>74</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22752,7 +22762,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22772,10 +22782,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B202" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22798,7 +22808,7 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22851,7 +22861,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -22871,10 +22881,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B203" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22897,7 +22907,7 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22950,7 +22960,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -22970,14 +22980,12 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B204" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="B204" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C204" t="s" s="2">
-        <v>544</v>
-      </c>
+      <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
         <v>74</v>
       </c>
@@ -22998,11 +23006,9 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L204" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="L204" s="2"/>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -23053,13 +23059,13 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>458</v>
+        <v>545</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>74</v>
@@ -23076,15 +23082,15 @@
         <v>546</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E205" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
         <v>80</v>
       </c>
@@ -23101,12 +23107,12 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L205" s="2"/>
-      <c r="M205" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="L205" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M205" s="2"/>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -23132,11 +23138,13 @@
         <v>74</v>
       </c>
       <c r="X205" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y205" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y205" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z205" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>74</v>
@@ -23154,13 +23162,13 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>89</v>
+        <v>461</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>74</v>
@@ -23174,21 +23182,23 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E206" s="2"/>
+      <c r="E206" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>74</v>
@@ -23200,11 +23210,11 @@
         <v>74</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -23231,13 +23241,11 @@
         <v>74</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y206" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>74</v>
@@ -23255,13 +23263,13 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>74</v>
@@ -23275,10 +23283,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23289,7 +23297,7 @@
         <v>80</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>74</v>
@@ -23301,11 +23309,11 @@
         <v>74</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L207" s="2"/>
       <c r="M207" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -23356,19 +23364,19 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>74</v>
@@ -23376,18 +23384,16 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E208" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>80</v>
       </c>
@@ -23404,11 +23410,11 @@
         <v>74</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -23435,11 +23441,13 @@
         <v>74</v>
       </c>
       <c r="X208" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y208" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y208" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z208" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>74</v>
@@ -23457,7 +23465,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -23469,7 +23477,7 @@
         <v>74</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>74</v>
@@ -23477,17 +23485,17 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E209" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F209" t="s" s="2">
         <v>80</v>
@@ -23505,11 +23513,11 @@
         <v>74</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -23536,13 +23544,11 @@
         <v>74</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y209" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y209" s="2"/>
       <c r="Z209" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>74</v>
@@ -23560,7 +23566,7 @@
         <v>74</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -23580,17 +23586,17 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E210" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F210" t="s" s="2">
         <v>80</v>
@@ -23608,11 +23614,11 @@
         <v>74</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -23663,7 +23669,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23683,20 +23689,20 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E211" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F211" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>75</v>
@@ -23711,11 +23717,11 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
@@ -23724,7 +23730,7 @@
       </c>
       <c r="Q211" s="2"/>
       <c r="R211" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S211" t="s" s="2">
         <v>74</v>
@@ -23766,7 +23772,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23786,17 +23792,17 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E212" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F212" t="s" s="2">
         <v>75</v>
@@ -23814,11 +23820,11 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -23827,7 +23833,7 @@
       </c>
       <c r="Q212" s="2"/>
       <c r="R212" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S212" t="s" s="2">
         <v>74</v>
@@ -23869,7 +23875,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23889,21 +23895,23 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E213" s="2"/>
+      <c r="E213" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F213" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>74</v>
@@ -23915,11 +23923,11 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -23970,13 +23978,13 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>74</v>
@@ -23990,10 +23998,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24001,10 +24009,10 @@
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>74</v>
@@ -24016,10 +24024,12 @@
         <v>74</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L214" s="2"/>
-      <c r="M214" s="2"/>
+      <c r="M214" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -24030,7 +24040,7 @@
         <v>74</v>
       </c>
       <c r="S214" t="s" s="2">
-        <v>556</v>
+        <v>74</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>74</v>
@@ -24045,11 +24055,13 @@
         <v>74</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y214" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y214" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z214" t="s" s="2">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>74</v>
@@ -24067,13 +24079,13 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>486</v>
+        <v>125</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>74</v>
@@ -24087,10 +24099,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24098,7 +24110,7 @@
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G215" t="s" s="2">
         <v>75</v>
@@ -24113,12 +24125,10 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L215" s="2"/>
-      <c r="M215" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="M215" s="2"/>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
@@ -24129,7 +24139,7 @@
         <v>74</v>
       </c>
       <c r="S215" t="s" s="2">
-        <v>33</v>
+        <v>559</v>
       </c>
       <c r="T215" t="s" s="2">
         <v>74</v>
@@ -24144,13 +24154,11 @@
         <v>74</v>
       </c>
       <c r="X215" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y215" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>74</v>
+        <v>488</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>74</v>
@@ -24168,10 +24176,10 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>75</v>
@@ -24188,10 +24196,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24218,19 +24226,19 @@
       </c>
       <c r="L216" s="2"/>
       <c r="M216" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
-        <v>494</v>
+        <v>74</v>
       </c>
       <c r="Q216" s="2"/>
       <c r="R216" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S216" t="s" s="2">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="T216" t="s" s="2">
         <v>74</v>
@@ -24269,7 +24277,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -24289,10 +24297,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24318,11 +24326,13 @@
         <v>107</v>
       </c>
       <c r="L217" s="2"/>
-      <c r="M217" s="2"/>
+      <c r="M217" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
@@ -24388,7 +24398,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>500</v>
@@ -24414,7 +24424,7 @@
         <v>74</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>501</v>
+        <v>107</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24467,7 +24477,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -24487,10 +24497,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24513,7 +24523,7 @@
         <v>74</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24566,7 +24576,7 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -24586,10 +24596,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24612,7 +24622,7 @@
         <v>74</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24665,7 +24675,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
@@ -24685,10 +24695,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24711,7 +24721,7 @@
         <v>74</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24764,7 +24774,7 @@
         <v>74</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -24784,10 +24794,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24810,7 +24820,7 @@
         <v>74</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>565</v>
+        <v>516</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24863,7 +24873,7 @@
         <v>74</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -24883,10 +24893,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24909,7 +24919,7 @@
         <v>74</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>521</v>
+        <v>568</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24962,7 +24972,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -24982,10 +24992,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25008,7 +25018,7 @@
         <v>74</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -25061,7 +25071,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -25081,10 +25091,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25107,7 +25117,7 @@
         <v>74</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -25160,7 +25170,7 @@
         <v>74</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -25180,10 +25190,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25206,7 +25216,7 @@
         <v>74</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -25259,7 +25269,7 @@
         <v>74</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -25279,10 +25289,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25305,7 +25315,7 @@
         <v>74</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -25358,7 +25368,7 @@
         <v>74</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -25378,10 +25388,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25404,7 +25414,7 @@
         <v>74</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25457,7 +25467,7 @@
         <v>74</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -25477,14 +25487,12 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>74</v>
       </c>
@@ -25505,11 +25513,9 @@
         <v>74</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="L229" s="2"/>
       <c r="M229" s="2"/>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -25560,13 +25566,13 @@
         <v>74</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>458</v>
+        <v>545</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>74</v>
@@ -25583,15 +25589,15 @@
         <v>575</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C230" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C230" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="D230" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E230" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>80</v>
       </c>
@@ -25608,12 +25614,12 @@
         <v>74</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L230" s="2"/>
-      <c r="M230" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="L230" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M230" s="2"/>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -25639,11 +25645,13 @@
         <v>74</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y230" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y230" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z230" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>74</v>
@@ -25661,13 +25669,13 @@
         <v>74</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>89</v>
+        <v>461</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>74</v>
@@ -25681,21 +25689,23 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E231" s="2"/>
+      <c r="E231" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F231" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>74</v>
@@ -25707,11 +25717,11 @@
         <v>74</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -25738,13 +25748,11 @@
         <v>74</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>74</v>
@@ -25762,13 +25770,13 @@
         <v>74</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>74</v>
@@ -25782,10 +25790,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25796,7 +25804,7 @@
         <v>80</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>74</v>
@@ -25808,11 +25816,11 @@
         <v>74</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -25863,19 +25871,19 @@
         <v>74</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK232" t="s" s="2">
         <v>74</v>
@@ -25883,18 +25891,16 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E233" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
         <v>80</v>
       </c>
@@ -25911,11 +25917,11 @@
         <v>74</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -25942,11 +25948,13 @@
         <v>74</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y233" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y233" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z233" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>74</v>
@@ -25964,7 +25972,7 @@
         <v>74</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -25976,7 +25984,7 @@
         <v>74</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>74</v>
@@ -25984,17 +25992,17 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E234" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F234" t="s" s="2">
         <v>80</v>
@@ -26012,11 +26020,11 @@
         <v>74</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -26043,13 +26051,11 @@
         <v>74</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>74</v>
@@ -26067,7 +26073,7 @@
         <v>74</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -26087,17 +26093,17 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E235" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F235" t="s" s="2">
         <v>80</v>
@@ -26115,11 +26121,11 @@
         <v>74</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -26170,7 +26176,7 @@
         <v>74</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -26190,20 +26196,20 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E236" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F236" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G236" t="s" s="2">
         <v>75</v>
@@ -26218,11 +26224,11 @@
         <v>74</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -26231,7 +26237,7 @@
       </c>
       <c r="Q236" s="2"/>
       <c r="R236" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S236" t="s" s="2">
         <v>74</v>
@@ -26273,7 +26279,7 @@
         <v>74</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
@@ -26293,17 +26299,17 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E237" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F237" t="s" s="2">
         <v>75</v>
@@ -26321,11 +26327,11 @@
         <v>74</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -26334,7 +26340,7 @@
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S237" t="s" s="2">
         <v>74</v>
@@ -26376,7 +26382,7 @@
         <v>74</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
@@ -26396,21 +26402,23 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E238" s="2"/>
+      <c r="E238" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F238" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>74</v>
@@ -26422,11 +26430,11 @@
         <v>74</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L238" s="2"/>
       <c r="M238" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -26477,13 +26485,13 @@
         <v>74</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>74</v>
@@ -26497,10 +26505,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26508,10 +26516,10 @@
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>74</v>
@@ -26523,10 +26531,12 @@
         <v>74</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L239" s="2"/>
-      <c r="M239" s="2"/>
+      <c r="M239" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -26537,7 +26547,7 @@
         <v>74</v>
       </c>
       <c r="S239" t="s" s="2">
-        <v>585</v>
+        <v>74</v>
       </c>
       <c r="T239" t="s" s="2">
         <v>74</v>
@@ -26552,11 +26562,13 @@
         <v>74</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y239" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y239" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z239" t="s" s="2">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>74</v>
@@ -26574,13 +26586,13 @@
         <v>74</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>486</v>
+        <v>125</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI239" t="s" s="2">
         <v>74</v>
@@ -26594,10 +26606,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26605,7 +26617,7 @@
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G240" t="s" s="2">
         <v>75</v>
@@ -26620,12 +26632,10 @@
         <v>74</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L240" s="2"/>
-      <c r="M240" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="M240" s="2"/>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
@@ -26636,7 +26646,7 @@
         <v>74</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>494</v>
+        <v>588</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>74</v>
@@ -26651,13 +26661,11 @@
         <v>74</v>
       </c>
       <c r="X240" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
-        <v>74</v>
+        <v>488</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>74</v>
@@ -26675,10 +26683,10 @@
         <v>74</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH240" t="s" s="2">
         <v>75</v>
@@ -26695,10 +26703,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26725,19 +26733,19 @@
       </c>
       <c r="L241" s="2"/>
       <c r="M241" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
-        <v>494</v>
+        <v>74</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S241" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>74</v>
@@ -26776,7 +26784,7 @@
         <v>74</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>80</v>
@@ -26796,10 +26804,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26825,11 +26833,13 @@
         <v>107</v>
       </c>
       <c r="L242" s="2"/>
-      <c r="M242" s="2"/>
+      <c r="M242" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
@@ -26895,7 +26905,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>500</v>
@@ -26921,7 +26931,7 @@
         <v>74</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>501</v>
+        <v>107</v>
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
@@ -26974,7 +26984,7 @@
         <v>74</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -26994,10 +27004,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27020,7 +27030,7 @@
         <v>74</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -27073,7 +27083,7 @@
         <v>74</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
@@ -27093,10 +27103,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27119,7 +27129,7 @@
         <v>74</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -27172,7 +27182,7 @@
         <v>74</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
@@ -27192,10 +27202,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27218,7 +27228,7 @@
         <v>74</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27271,7 +27281,7 @@
         <v>74</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -27291,10 +27301,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27317,7 +27327,7 @@
         <v>74</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>594</v>
+        <v>516</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -27370,7 +27380,7 @@
         <v>74</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>80</v>
@@ -27390,10 +27400,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27416,7 +27426,7 @@
         <v>74</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>521</v>
+        <v>597</v>
       </c>
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
@@ -27469,7 +27479,7 @@
         <v>74</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>80</v>
@@ -27489,10 +27499,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27515,7 +27525,7 @@
         <v>74</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
@@ -27568,7 +27578,7 @@
         <v>74</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
@@ -27588,10 +27598,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27614,7 +27624,7 @@
         <v>74</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
@@ -27667,7 +27677,7 @@
         <v>74</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>80</v>
@@ -27687,10 +27697,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -27713,7 +27723,7 @@
         <v>74</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
@@ -27766,7 +27776,7 @@
         <v>74</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -27786,10 +27796,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -27812,7 +27822,7 @@
         <v>74</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
@@ -27865,7 +27875,7 @@
         <v>74</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>80</v>
@@ -27885,10 +27895,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -27911,7 +27921,7 @@
         <v>74</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
@@ -27964,7 +27974,7 @@
         <v>74</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>80</v>
@@ -27984,14 +27994,12 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
         <v>74</v>
       </c>
@@ -28012,11 +28020,9 @@
         <v>74</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L254" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="L254" s="2"/>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -28067,13 +28073,13 @@
         <v>74</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>458</v>
+        <v>545</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI254" t="s" s="2">
         <v>74</v>
@@ -28090,15 +28096,15 @@
         <v>604</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C255" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C255" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="D255" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E255" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
         <v>80</v>
       </c>
@@ -28115,12 +28121,12 @@
         <v>74</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L255" s="2"/>
-      <c r="M255" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="L255" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M255" s="2"/>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
@@ -28146,11 +28152,13 @@
         <v>74</v>
       </c>
       <c r="X255" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y255" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y255" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z255" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>74</v>
@@ -28168,13 +28176,13 @@
         <v>74</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>89</v>
+        <v>461</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI255" t="s" s="2">
         <v>74</v>
@@ -28188,21 +28196,23 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E256" s="2"/>
+      <c r="E256" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F256" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>74</v>
@@ -28214,11 +28224,11 @@
         <v>74</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L256" s="2"/>
       <c r="M256" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N256" s="2"/>
       <c r="O256" s="2"/>
@@ -28245,13 +28255,11 @@
         <v>74</v>
       </c>
       <c r="X256" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y256" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>74</v>
@@ -28269,13 +28277,13 @@
         <v>74</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI256" t="s" s="2">
         <v>74</v>
@@ -28289,10 +28297,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28303,7 +28311,7 @@
         <v>80</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H257" t="s" s="2">
         <v>74</v>
@@ -28315,11 +28323,11 @@
         <v>74</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L257" s="2"/>
       <c r="M257" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -28370,19 +28378,19 @@
         <v>74</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>74</v>
@@ -28390,18 +28398,16 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E258" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
         <v>80</v>
       </c>
@@ -28418,11 +28424,11 @@
         <v>74</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L258" s="2"/>
       <c r="M258" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" s="2"/>
@@ -28449,11 +28455,13 @@
         <v>74</v>
       </c>
       <c r="X258" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y258" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y258" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z258" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA258" t="s" s="2">
         <v>74</v>
@@ -28471,7 +28479,7 @@
         <v>74</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -28483,7 +28491,7 @@
         <v>74</v>
       </c>
       <c r="AJ258" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK258" t="s" s="2">
         <v>74</v>
@@ -28491,17 +28499,17 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E259" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F259" t="s" s="2">
         <v>80</v>
@@ -28519,11 +28527,11 @@
         <v>74</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L259" s="2"/>
       <c r="M259" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -28550,13 +28558,11 @@
         <v>74</v>
       </c>
       <c r="X259" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y259" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y259" s="2"/>
       <c r="Z259" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>74</v>
@@ -28574,7 +28580,7 @@
         <v>74</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
@@ -28594,17 +28600,17 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E260" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F260" t="s" s="2">
         <v>80</v>
@@ -28622,11 +28628,11 @@
         <v>74</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L260" s="2"/>
       <c r="M260" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N260" s="2"/>
       <c r="O260" s="2"/>
@@ -28677,7 +28683,7 @@
         <v>74</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>80</v>
@@ -28697,20 +28703,20 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E261" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F261" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G261" t="s" s="2">
         <v>75</v>
@@ -28725,11 +28731,11 @@
         <v>74</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L261" s="2"/>
       <c r="M261" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N261" s="2"/>
       <c r="O261" s="2"/>
@@ -28738,7 +28744,7 @@
       </c>
       <c r="Q261" s="2"/>
       <c r="R261" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S261" t="s" s="2">
         <v>74</v>
@@ -28780,7 +28786,7 @@
         <v>74</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>80</v>
@@ -28800,17 +28806,17 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E262" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F262" t="s" s="2">
         <v>75</v>
@@ -28828,11 +28834,11 @@
         <v>74</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L262" s="2"/>
       <c r="M262" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N262" s="2"/>
       <c r="O262" s="2"/>
@@ -28841,7 +28847,7 @@
       </c>
       <c r="Q262" s="2"/>
       <c r="R262" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S262" t="s" s="2">
         <v>74</v>
@@ -28883,7 +28889,7 @@
         <v>74</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>80</v>
@@ -28903,21 +28909,23 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E263" s="2"/>
+      <c r="E263" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F263" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H263" t="s" s="2">
         <v>74</v>
@@ -28929,11 +28937,11 @@
         <v>74</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L263" s="2"/>
       <c r="M263" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -28984,13 +28992,13 @@
         <v>74</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI263" t="s" s="2">
         <v>74</v>
@@ -29004,10 +29012,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -29015,10 +29023,10 @@
       </c>
       <c r="E264" s="2"/>
       <c r="F264" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G264" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H264" t="s" s="2">
         <v>74</v>
@@ -29030,10 +29038,12 @@
         <v>74</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L264" s="2"/>
-      <c r="M264" s="2"/>
+      <c r="M264" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
@@ -29044,7 +29054,7 @@
         <v>74</v>
       </c>
       <c r="S264" t="s" s="2">
-        <v>585</v>
+        <v>74</v>
       </c>
       <c r="T264" t="s" s="2">
         <v>74</v>
@@ -29059,11 +29069,13 @@
         <v>74</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y264" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y264" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z264" t="s" s="2">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>74</v>
@@ -29081,13 +29093,13 @@
         <v>74</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>486</v>
+        <v>125</v>
       </c>
       <c r="AG264" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH264" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI264" t="s" s="2">
         <v>74</v>
@@ -29101,10 +29113,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29112,7 +29124,7 @@
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G265" t="s" s="2">
         <v>75</v>
@@ -29127,12 +29139,10 @@
         <v>74</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L265" s="2"/>
-      <c r="M265" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="M265" s="2"/>
       <c r="N265" s="2"/>
       <c r="O265" s="2"/>
       <c r="P265" t="s" s="2">
@@ -29143,7 +29153,7 @@
         <v>74</v>
       </c>
       <c r="S265" t="s" s="2">
-        <v>494</v>
+        <v>588</v>
       </c>
       <c r="T265" t="s" s="2">
         <v>74</v>
@@ -29158,13 +29168,11 @@
         <v>74</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y265" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y265" s="2"/>
       <c r="Z265" t="s" s="2">
-        <v>74</v>
+        <v>488</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>74</v>
@@ -29182,10 +29190,10 @@
         <v>74</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG265" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH265" t="s" s="2">
         <v>75</v>
@@ -29202,10 +29210,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -29232,19 +29240,19 @@
       </c>
       <c r="L266" s="2"/>
       <c r="M266" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" s="2"/>
       <c r="P266" t="s" s="2">
-        <v>494</v>
+        <v>74</v>
       </c>
       <c r="Q266" s="2"/>
       <c r="R266" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S266" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="T266" t="s" s="2">
         <v>74</v>
@@ -29283,7 +29291,7 @@
         <v>74</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>80</v>
@@ -29303,10 +29311,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -29332,11 +29340,13 @@
         <v>107</v>
       </c>
       <c r="L267" s="2"/>
-      <c r="M267" s="2"/>
+      <c r="M267" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="Q267" s="2"/>
       <c r="R267" t="s" s="2">
@@ -29402,7 +29412,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>500</v>
@@ -29428,7 +29438,7 @@
         <v>74</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>501</v>
+        <v>107</v>
       </c>
       <c r="L268" s="2"/>
       <c r="M268" s="2"/>
@@ -29481,7 +29491,7 @@
         <v>74</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>80</v>
@@ -29501,10 +29511,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29527,7 +29537,7 @@
         <v>74</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
@@ -29580,7 +29590,7 @@
         <v>74</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>80</v>
@@ -29600,10 +29610,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29626,7 +29636,7 @@
         <v>74</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
@@ -29679,7 +29689,7 @@
         <v>74</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>80</v>
@@ -29699,10 +29709,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -29725,7 +29735,7 @@
         <v>74</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
@@ -29778,7 +29788,7 @@
         <v>74</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>80</v>
@@ -29798,10 +29808,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -29824,7 +29834,7 @@
         <v>74</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>622</v>
+        <v>516</v>
       </c>
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
@@ -29877,7 +29887,7 @@
         <v>74</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>80</v>
@@ -29897,10 +29907,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -29923,7 +29933,7 @@
         <v>74</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>521</v>
+        <v>625</v>
       </c>
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
@@ -29976,7 +29986,7 @@
         <v>74</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>80</v>
@@ -29996,10 +30006,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30022,7 +30032,7 @@
         <v>74</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
@@ -30075,7 +30085,7 @@
         <v>74</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>80</v>
@@ -30095,10 +30105,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30121,7 +30131,7 @@
         <v>74</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
@@ -30174,7 +30184,7 @@
         <v>74</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>80</v>
@@ -30194,10 +30204,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30220,7 +30230,7 @@
         <v>74</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
@@ -30273,7 +30283,7 @@
         <v>74</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>80</v>
@@ -30293,10 +30303,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -30319,7 +30329,7 @@
         <v>74</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
@@ -30372,7 +30382,7 @@
         <v>74</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>80</v>
@@ -30392,10 +30402,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -30418,7 +30428,7 @@
         <v>74</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
@@ -30471,7 +30481,7 @@
         <v>74</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>80</v>
@@ -30491,10 +30501,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>629</v>
+        <v>543</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30505,7 +30515,7 @@
         <v>80</v>
       </c>
       <c r="G279" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H279" t="s" s="2">
         <v>74</v>
@@ -30517,7 +30527,7 @@
         <v>74</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>630</v>
+        <v>544</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30570,13 +30580,13 @@
         <v>74</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>629</v>
+        <v>545</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI279" t="s" s="2">
         <v>74</v>
@@ -30590,10 +30600,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -30616,7 +30626,7 @@
         <v>74</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
@@ -30669,7 +30679,7 @@
         <v>74</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>80</v>
@@ -30689,10 +30699,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -30715,7 +30725,7 @@
         <v>74</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
@@ -30768,7 +30778,7 @@
         <v>74</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>80</v>
@@ -30788,10 +30798,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -30814,12 +30824,10 @@
         <v>74</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L282" s="2"/>
-      <c r="M282" t="s" s="2">
-        <v>637</v>
-      </c>
+      <c r="M282" s="2"/>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
@@ -30869,7 +30877,7 @@
         <v>74</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>80</v>
@@ -30898,14 +30906,12 @@
       <c r="D283" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E283" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E283" s="2"/>
       <c r="F283" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G283" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>74</v>
@@ -30917,11 +30923,11 @@
         <v>74</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>85</v>
+        <v>639</v>
       </c>
       <c r="L283" s="2"/>
       <c r="M283" t="s" s="2">
-        <v>86</v>
+        <v>640</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -30948,11 +30954,13 @@
         <v>74</v>
       </c>
       <c r="X283" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y283" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y283" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z283" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA283" t="s" s="2">
         <v>74</v>
@@ -30970,13 +30978,13 @@
         <v>74</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>89</v>
+        <v>638</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH283" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI283" t="s" s="2">
         <v>74</v>
@@ -30990,21 +30998,23 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E284" s="2"/>
+      <c r="E284" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F284" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G284" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H284" t="s" s="2">
         <v>74</v>
@@ -31016,11 +31026,11 @@
         <v>74</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L284" s="2"/>
       <c r="M284" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
@@ -31047,13 +31057,11 @@
         <v>74</v>
       </c>
       <c r="X284" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y284" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y284" s="2"/>
       <c r="Z284" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA284" t="s" s="2">
         <v>74</v>
@@ -31071,13 +31079,13 @@
         <v>74</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH284" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI284" t="s" s="2">
         <v>74</v>
@@ -31091,10 +31099,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -31105,7 +31113,7 @@
         <v>80</v>
       </c>
       <c r="G285" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H285" t="s" s="2">
         <v>74</v>
@@ -31117,11 +31125,11 @@
         <v>74</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L285" s="2"/>
       <c r="M285" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N285" s="2"/>
       <c r="O285" s="2"/>
@@ -31172,19 +31180,19 @@
         <v>74</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH285" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI285" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ285" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK285" t="s" s="2">
         <v>74</v>
@@ -31192,18 +31200,16 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E286" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E286" s="2"/>
       <c r="F286" t="s" s="2">
         <v>80</v>
       </c>
@@ -31220,11 +31226,11 @@
         <v>74</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L286" s="2"/>
       <c r="M286" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" s="2"/>
@@ -31251,11 +31257,13 @@
         <v>74</v>
       </c>
       <c r="X286" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y286" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y286" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z286" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA286" t="s" s="2">
         <v>74</v>
@@ -31273,7 +31281,7 @@
         <v>74</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>80</v>
@@ -31285,7 +31293,7 @@
         <v>74</v>
       </c>
       <c r="AJ286" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK286" t="s" s="2">
         <v>74</v>
@@ -31293,17 +31301,17 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E287" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F287" t="s" s="2">
         <v>80</v>
@@ -31321,11 +31329,11 @@
         <v>74</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L287" s="2"/>
       <c r="M287" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -31352,13 +31360,11 @@
         <v>74</v>
       </c>
       <c r="X287" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y287" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>74</v>
@@ -31376,7 +31382,7 @@
         <v>74</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>80</v>
@@ -31396,17 +31402,17 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E288" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F288" t="s" s="2">
         <v>80</v>
@@ -31424,11 +31430,11 @@
         <v>74</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L288" s="2"/>
       <c r="M288" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N288" s="2"/>
       <c r="O288" s="2"/>
@@ -31479,7 +31485,7 @@
         <v>74</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>80</v>
@@ -31499,20 +31505,20 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E289" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F289" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G289" t="s" s="2">
         <v>75</v>
@@ -31527,11 +31533,11 @@
         <v>74</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L289" s="2"/>
       <c r="M289" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -31540,7 +31546,7 @@
       </c>
       <c r="Q289" s="2"/>
       <c r="R289" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S289" t="s" s="2">
         <v>74</v>
@@ -31582,7 +31588,7 @@
         <v>74</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>80</v>
@@ -31602,17 +31608,17 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E290" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F290" t="s" s="2">
         <v>75</v>
@@ -31630,11 +31636,11 @@
         <v>74</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L290" s="2"/>
       <c r="M290" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N290" s="2"/>
       <c r="O290" s="2"/>
@@ -31643,7 +31649,7 @@
       </c>
       <c r="Q290" s="2"/>
       <c r="R290" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S290" t="s" s="2">
         <v>74</v>
@@ -31685,7 +31691,7 @@
         <v>74</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>80</v>
@@ -31705,21 +31711,23 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E291" s="2"/>
+      <c r="E291" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F291" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G291" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H291" t="s" s="2">
         <v>74</v>
@@ -31731,11 +31739,11 @@
         <v>74</v>
       </c>
       <c r="K291" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L291" s="2"/>
       <c r="M291" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N291" s="2"/>
       <c r="O291" s="2"/>
@@ -31786,13 +31794,13 @@
         <v>74</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH291" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI291" t="s" s="2">
         <v>74</v>
@@ -31806,10 +31814,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -31820,7 +31828,7 @@
         <v>80</v>
       </c>
       <c r="G292" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H292" t="s" s="2">
         <v>74</v>
@@ -31832,10 +31840,12 @@
         <v>74</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L292" s="2"/>
-      <c r="M292" s="2"/>
+      <c r="M292" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N292" s="2"/>
       <c r="O292" s="2"/>
       <c r="P292" t="s" s="2">
@@ -31843,7 +31853,7 @@
       </c>
       <c r="Q292" s="2"/>
       <c r="R292" t="s" s="2">
-        <v>648</v>
+        <v>74</v>
       </c>
       <c r="S292" t="s" s="2">
         <v>74</v>
@@ -31861,11 +31871,13 @@
         <v>74</v>
       </c>
       <c r="X292" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y292" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y292" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z292" t="s" s="2">
-        <v>649</v>
+        <v>74</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>74</v>
@@ -31883,13 +31895,13 @@
         <v>74</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>647</v>
+        <v>125</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH292" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI292" t="s" s="2">
         <v>74</v>
@@ -31914,7 +31926,7 @@
       </c>
       <c r="E293" s="2"/>
       <c r="F293" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G293" t="s" s="2">
         <v>75</v>
@@ -31929,7 +31941,7 @@
         <v>74</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>651</v>
+        <v>85</v>
       </c>
       <c r="L293" s="2"/>
       <c r="M293" s="2"/>
@@ -31940,7 +31952,7 @@
       </c>
       <c r="Q293" s="2"/>
       <c r="R293" t="s" s="2">
-        <v>74</v>
+        <v>651</v>
       </c>
       <c r="S293" t="s" s="2">
         <v>74</v>
@@ -31958,13 +31970,11 @@
         <v>74</v>
       </c>
       <c r="X293" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y293" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>74</v>
+        <v>652</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>74</v>
@@ -31985,7 +31995,7 @@
         <v>650</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>75</v>
@@ -32002,10 +32012,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -32013,10 +32023,10 @@
       </c>
       <c r="E294" s="2"/>
       <c r="F294" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G294" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H294" t="s" s="2">
         <v>74</v>
@@ -32028,7 +32038,7 @@
         <v>74</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
@@ -32081,26 +32091,125 @@
         <v>74</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH294" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ294" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK294" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="295" hidden="true">
+      <c r="A295" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="D295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E295" s="2"/>
+      <c r="F295" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G295" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ294" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK294" t="s" s="2">
+      <c r="H295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K295" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L295" s="2"/>
+      <c r="M295" s="2"/>
+      <c r="N295" s="2"/>
+      <c r="O295" s="2"/>
+      <c r="P295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q295" s="2"/>
+      <c r="R295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF295" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG295" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH295" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ295" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK295" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK294">
+  <autoFilter ref="A1:AK295">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -32110,7 +32219,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI293">
+  <conditionalFormatting sqref="A2:AI294">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
